--- a/app/templates/Recepciones/F-LEM-P-01.05 V04 RECEPCIÓN DE MUESTRAS DE ALBAÑILERIA.xlsx
+++ b/app/templates/Recepciones/F-LEM-P-01.05 V04 RECEPCIÓN DE MUESTRAS DE ALBAÑILERIA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64DEA2D-0196-4B17-9EAE-061E1DE8CE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1B1FA5-22E6-4390-ADE2-B0EE9498960C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -352,13 +352,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -426,6 +419,12 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -592,12 +591,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -607,10 +606,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -631,21 +626,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -658,7 +644,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -667,45 +653,36 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -718,13 +695,13 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -736,37 +713,30 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -774,142 +744,172 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="9"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="9"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="9"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1343,7 +1343,7 @@
     <col min="3" max="3" width="1.6640625" style="4" customWidth="1"/>
     <col min="4" max="4" width="11.88671875" style="4" customWidth="1"/>
     <col min="5" max="5" width="14.33203125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="22.88671875" style="4" customWidth="1"/>
     <col min="8" max="8" width="16.44140625" style="4" customWidth="1"/>
     <col min="9" max="9" width="11" style="4" customWidth="1"/>
@@ -1353,807 +1353,826 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73"/>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="86" t="s">
+      <c r="A1" s="58"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="8" t="s">
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="39" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="40">
+      <c r="L2" s="33">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="39" t="s">
+      <c r="A3" s="61"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="41">
+      <c r="L3" s="34">
         <v>44937</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="79"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="8" t="s">
+      <c r="A4" s="64"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
     </row>
     <row r="6" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="29" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="42"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="35"/>
     </row>
     <row r="7" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="43"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="42"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="35"/>
     </row>
     <row r="8" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="44" t="s">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="30"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="42"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="35"/>
     </row>
     <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
     </row>
     <row r="10" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="83"/>
     </row>
     <row r="11" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="14" t="s">
+      <c r="B11" s="22"/>
+      <c r="C11" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
     </row>
     <row r="12" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="22"/>
+      <c r="C12" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="83"/>
     </row>
     <row r="13" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="70"/>
-      <c r="C13" s="14" t="s">
+      <c r="B13" s="78"/>
+      <c r="C13" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="83"/>
     </row>
     <row r="14" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="22"/>
+      <c r="C14" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="54"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="56" t="s">
+      <c r="D14" s="83"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="54"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
     </row>
     <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
     </row>
     <row r="16" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="14" t="s">
+      <c r="B16" s="22"/>
+      <c r="C16" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="70"/>
-      <c r="C17" s="14" t="s">
+      <c r="B17" s="78"/>
+      <c r="C17" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
       <c r="M17" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="14" t="s">
+      <c r="B18" s="22"/>
+      <c r="C18" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="54"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="55"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
     </row>
     <row r="19" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="14" t="s">
+      <c r="B19" s="22"/>
+      <c r="C19" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="54"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
     </row>
     <row r="20" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="13"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="84"/>
     </row>
     <row r="21" spans="1:15" ht="62.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="83" t="s">
+      <c r="B21" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="85"/>
-      <c r="D21" s="83" t="s">
+      <c r="C21" s="87"/>
+      <c r="D21" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="84"/>
-      <c r="F21" s="84"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="17" t="s">
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="95" t="s">
+      <c r="I21" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="95"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="18" t="s">
+      <c r="J21" s="90"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="91" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="60"/>
-      <c r="B22" s="63"/>
-      <c r="C22" s="64"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="51"/>
+      <c r="A22" s="92"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="94"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="96"/>
+      <c r="F22" s="96"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="98"/>
+      <c r="I22" s="99"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="99"/>
+      <c r="L22" s="100"/>
     </row>
     <row r="23" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="60"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="51"/>
+      <c r="A23" s="92"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="95"/>
+      <c r="E23" s="96"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="97"/>
+      <c r="H23" s="98"/>
+      <c r="I23" s="99"/>
+      <c r="J23" s="99"/>
+      <c r="K23" s="99"/>
+      <c r="L23" s="100"/>
     </row>
     <row r="24" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="60"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="51"/>
+      <c r="A24" s="92"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="97"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="99"/>
+      <c r="L24" s="100"/>
     </row>
     <row r="25" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="60"/>
-      <c r="B25" s="63"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="51"/>
+      <c r="A25" s="92"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="97"/>
+      <c r="H25" s="98"/>
+      <c r="I25" s="99"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="99"/>
+      <c r="L25" s="100"/>
     </row>
     <row r="26" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="60"/>
-      <c r="B26" s="63"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="51"/>
+      <c r="A26" s="92"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="94"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="97"/>
+      <c r="H26" s="98"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="99"/>
+      <c r="L26" s="100"/>
     </row>
     <row r="27" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="60"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="51"/>
+      <c r="A27" s="92"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="96"/>
+      <c r="F27" s="96"/>
+      <c r="G27" s="97"/>
+      <c r="H27" s="98"/>
+      <c r="I27" s="99"/>
+      <c r="J27" s="99"/>
+      <c r="K27" s="99"/>
+      <c r="L27" s="100"/>
     </row>
     <row r="28" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="61"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="64"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="51"/>
+      <c r="A28" s="98"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="95"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="98"/>
+      <c r="I28" s="99"/>
+      <c r="J28" s="99"/>
+      <c r="K28" s="99"/>
+      <c r="L28" s="100"/>
     </row>
     <row r="29" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="61"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="64"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="51"/>
+      <c r="A29" s="98"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="97"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="99"/>
+      <c r="J29" s="99"/>
+      <c r="K29" s="99"/>
+      <c r="L29" s="100"/>
     </row>
     <row r="30" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="61"/>
-      <c r="B30" s="63"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="51"/>
+      <c r="A30" s="98"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="98"/>
+      <c r="I30" s="99"/>
+      <c r="J30" s="99"/>
+      <c r="K30" s="99"/>
+      <c r="L30" s="100"/>
     </row>
     <row r="31" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="61"/>
-      <c r="B31" s="63"/>
-      <c r="C31" s="64"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="72"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="51"/>
+      <c r="A31" s="98"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="94"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="99"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="100"/>
     </row>
     <row r="32" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="61"/>
-      <c r="B32" s="63"/>
-      <c r="C32" s="64"/>
-      <c r="D32" s="67"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="68"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="72"/>
-      <c r="L32" s="51"/>
+      <c r="A32" s="98"/>
+      <c r="B32" s="93"/>
+      <c r="C32" s="94"/>
+      <c r="D32" s="95"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="99"/>
+      <c r="J32" s="99"/>
+      <c r="K32" s="99"/>
+      <c r="L32" s="100"/>
     </row>
     <row r="33" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="61"/>
-      <c r="B33" s="63"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="72"/>
-      <c r="K33" s="72"/>
-      <c r="L33" s="51"/>
+      <c r="A33" s="98"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="94"/>
+      <c r="D33" s="95"/>
+      <c r="E33" s="96"/>
+      <c r="F33" s="96"/>
+      <c r="G33" s="97"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="99"/>
+      <c r="K33" s="99"/>
+      <c r="L33" s="100"/>
     </row>
     <row r="34" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="61"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="72"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="51"/>
+      <c r="A34" s="98"/>
+      <c r="B34" s="93"/>
+      <c r="C34" s="94"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="99"/>
+      <c r="J34" s="99"/>
+      <c r="K34" s="99"/>
+      <c r="L34" s="100"/>
     </row>
     <row r="35" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="61"/>
-      <c r="B35" s="63"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72"/>
-      <c r="K35" s="72"/>
-      <c r="L35" s="51"/>
+      <c r="A35" s="98"/>
+      <c r="B35" s="93"/>
+      <c r="C35" s="94"/>
+      <c r="D35" s="95"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="96"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="98"/>
+      <c r="I35" s="99"/>
+      <c r="J35" s="99"/>
+      <c r="K35" s="99"/>
+      <c r="L35" s="100"/>
     </row>
     <row r="36" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A36" s="19"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="35" t="s">
+      <c r="A37" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="47"/>
-      <c r="I37" s="47"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="48"/>
-      <c r="L37" s="48"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="41"/>
+      <c r="L37" s="41"/>
     </row>
     <row r="38" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
     </row>
     <row r="39" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="35" t="s">
+      <c r="A39" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="99" t="s">
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="G39" s="98" t="s">
+      <c r="G39" s="53" t="s">
         <v>30</v>
       </c>
       <c r="H39" s="1"/>
-      <c r="I39" s="102"/>
-      <c r="J39" s="102"/>
-      <c r="K39" s="100" t="s">
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="L39" s="101"/>
+      <c r="L39" s="56"/>
     </row>
     <row r="40" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="38" t="s">
+      <c r="A40" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="36"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="99"/>
-      <c r="G40" s="98"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="53"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="102"/>
-      <c r="J40" s="102"/>
-      <c r="K40" s="100"/>
-      <c r="L40" s="101"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="56"/>
     </row>
     <row r="41" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A41" s="37"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="96" t="s">
+      <c r="A42" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="96"/>
-      <c r="C42" s="96"/>
-      <c r="D42" s="96"/>
-      <c r="E42" s="96"/>
-      <c r="F42" s="96"/>
-      <c r="G42" s="97"/>
-      <c r="H42" s="97"/>
-      <c r="I42" s="97"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
     </row>
     <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="96"/>
-      <c r="B43" s="96"/>
-      <c r="C43" s="96"/>
-      <c r="D43" s="96"/>
-      <c r="E43" s="96"/>
-      <c r="F43" s="96"/>
-      <c r="G43" s="97"/>
-      <c r="H43" s="97"/>
-      <c r="I43" s="97"/>
-      <c r="J43" s="22"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
+      <c r="A43" s="51"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
     </row>
     <row r="44" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A44" s="37"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
     </row>
     <row r="45" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="65" t="s">
+      <c r="A45" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="65"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="66" t="s">
+      <c r="B45" s="80"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="H45" s="66"/>
-      <c r="I45" s="59" t="s">
+      <c r="H45" s="81"/>
+      <c r="I45" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="J45" s="59"/>
+      <c r="J45" s="50"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
     </row>
     <row r="46" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="50"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="71" t="s">
+      <c r="B46" s="43"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="H46" s="71"/>
-      <c r="I46" s="59" t="s">
+      <c r="H46" s="77"/>
+      <c r="I46" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="J46" s="59"/>
+      <c r="J46" s="50"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="13"/>
+      <c r="L46" s="12"/>
     </row>
     <row r="47" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="23"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
       <c r="G47" s="2"/>
       <c r="H47" s="3"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="25"/>
-      <c r="K47" s="25"/>
-      <c r="L47" s="13"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="12"/>
     </row>
     <row r="48" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="82" t="s">
+      <c r="A48" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="82"/>
-      <c r="C48" s="82"/>
-      <c r="D48" s="82"/>
-      <c r="E48" s="82"/>
-      <c r="F48" s="82"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="82"/>
-      <c r="I48" s="82"/>
-      <c r="J48" s="82"/>
-      <c r="K48" s="82"/>
-      <c r="L48" s="82"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="67"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="67"/>
+      <c r="K48" s="67"/>
+      <c r="L48" s="67"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bTnFV5rhJNfXWIcWn7ED2Lo/UYo/z8FPwFRsu7PauAxXAKn7iwXghBYlQSG/D9hgtVZUjgZIGRjeBUAzLcqqpg==" saltValue="JDShMy1IUFUdMPQBYiYCiA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="60">
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="A42:F43"/>
-    <mergeCell ref="G42:I43"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="D22:G22"/>
     <mergeCell ref="I23:K23"/>
     <mergeCell ref="I24:K24"/>
     <mergeCell ref="A1:D4"/>
@@ -2170,38 +2189,18 @@
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="I21:K21"/>
     <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="A42:F43"/>
+    <mergeCell ref="G42:I43"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:G35"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>

--- a/app/templates/Recepciones/F-LEM-P-01.05 V04 RECEPCIÓN DE MUESTRAS DE ALBAÑILERIA.xlsx
+++ b/app/templates/Recepciones/F-LEM-P-01.05 V04 RECEPCIÓN DE MUESTRAS DE ALBAÑILERIA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1B1FA5-22E6-4390-ADE2-B0EE9498960C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE5CF0F-8DA6-4C99-9357-A0E967E4B508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -744,94 +744,52 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -841,75 +799,117 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="9"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="9"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1353,18 +1353,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58"/>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="68" t="s">
+      <c r="A1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="70"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="89"/>
       <c r="K1" s="7" t="s">
         <v>6</v>
       </c>
@@ -1373,16 +1373,16 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="73"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="92"/>
       <c r="K2" s="32" t="s">
         <v>7</v>
       </c>
@@ -1391,16 +1391,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="92"/>
       <c r="K3" s="32" t="s">
         <v>10</v>
       </c>
@@ -1409,16 +1409,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="95"/>
       <c r="K4" s="7" t="s">
         <v>8</v>
       </c>
@@ -1445,8 +1445,8 @@
         <v>19</v>
       </c>
       <c r="B6" s="13"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -1463,8 +1463,8 @@
         <v>20</v>
       </c>
       <c r="B7" s="13"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
       <c r="G7" s="36"/>
@@ -1505,8 +1505,8 @@
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
     </row>
     <row r="10" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
@@ -1516,15 +1516,15 @@
       <c r="C10" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="83"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="46"/>
       <c r="F10" s="46"/>
       <c r="G10" s="46"/>
       <c r="H10" s="46"/>
       <c r="I10" s="46"/>
       <c r="J10" s="46"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
@@ -1534,15 +1534,15 @@
       <c r="C11" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="83"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="46"/>
       <c r="F11" s="46"/>
       <c r="G11" s="46"/>
       <c r="H11" s="46"/>
       <c r="I11" s="46"/>
       <c r="J11" s="46"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
     </row>
     <row r="12" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
@@ -1552,33 +1552,33 @@
       <c r="C12" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="83"/>
+      <c r="D12" s="52"/>
       <c r="E12" s="46"/>
       <c r="F12" s="46"/>
       <c r="G12" s="46"/>
       <c r="H12" s="46"/>
       <c r="I12" s="46"/>
       <c r="J12" s="46"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
     </row>
     <row r="13" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="78"/>
+      <c r="B13" s="71"/>
       <c r="C13" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="83"/>
+      <c r="D13" s="52"/>
       <c r="E13" s="46"/>
       <c r="F13" s="46"/>
       <c r="G13" s="46"/>
       <c r="H13" s="46"/>
       <c r="I13" s="46"/>
       <c r="J13" s="46"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="52"/>
     </row>
     <row r="14" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
@@ -1588,7 +1588,7 @@
       <c r="C14" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="83"/>
+      <c r="D14" s="52"/>
       <c r="E14" s="46"/>
       <c r="F14" s="46"/>
       <c r="G14" s="46"/>
@@ -1596,7 +1596,7 @@
       <c r="I14" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="83"/>
+      <c r="J14" s="52"/>
       <c r="K14" s="46"/>
       <c r="L14" s="46"/>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B15" s="27"/>
       <c r="C15" s="13"/>
-      <c r="D15" s="82"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
@@ -1624,7 +1624,7 @@
       <c r="C16" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="83"/>
+      <c r="D16" s="52"/>
       <c r="E16" s="46"/>
       <c r="F16" s="46"/>
       <c r="G16" s="46"/>
@@ -1635,14 +1635,14 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="78"/>
+      <c r="B17" s="71"/>
       <c r="C17" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="83"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="46"/>
       <c r="F17" s="46"/>
       <c r="G17" s="46"/>
@@ -1663,7 +1663,7 @@
       <c r="C18" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="83"/>
+      <c r="D18" s="52"/>
       <c r="E18" s="46"/>
       <c r="F18" s="46"/>
       <c r="G18" s="46"/>
@@ -1681,7 +1681,7 @@
       <c r="C19" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="83"/>
+      <c r="D19" s="52"/>
       <c r="E19" s="46"/>
       <c r="F19" s="46"/>
       <c r="G19" s="46"/>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="84"/>
+      <c r="D20" s="53"/>
       <c r="E20" s="11"/>
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
@@ -1705,229 +1705,229 @@
       <c r="I20" s="14"/>
       <c r="J20" s="14"/>
       <c r="K20" s="14"/>
-      <c r="L20" s="84"/>
+      <c r="L20" s="53"/>
     </row>
     <row r="21" spans="1:15" ht="62.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="87"/>
-      <c r="D21" s="86" t="s">
+      <c r="C21" s="86"/>
+      <c r="D21" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="88"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="89" t="s">
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="86"/>
+      <c r="H21" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="90" t="s">
+      <c r="I21" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="90"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="91" t="s">
+      <c r="J21" s="96"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="55" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="92"/>
-      <c r="B22" s="93"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="96"/>
-      <c r="F22" s="96"/>
-      <c r="G22" s="97"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="99"/>
-      <c r="J22" s="99"/>
-      <c r="K22" s="99"/>
-      <c r="L22" s="100"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="62"/>
     </row>
     <row r="23" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="92"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="94"/>
-      <c r="D23" s="95"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="97"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="99"/>
-      <c r="J23" s="99"/>
-      <c r="K23" s="99"/>
-      <c r="L23" s="100"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="73"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="62"/>
     </row>
     <row r="24" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="92"/>
-      <c r="B24" s="93"/>
-      <c r="C24" s="94"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="97"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="100"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="62"/>
     </row>
     <row r="25" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="92"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="94"/>
-      <c r="D25" s="95"/>
-      <c r="E25" s="96"/>
-      <c r="F25" s="96"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="98"/>
-      <c r="I25" s="99"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="99"/>
-      <c r="L25" s="100"/>
+      <c r="A25" s="57"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="73"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="62"/>
     </row>
     <row r="26" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="92"/>
-      <c r="B26" s="93"/>
-      <c r="C26" s="94"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="96"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="98"/>
-      <c r="I26" s="99"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="99"/>
-      <c r="L26" s="100"/>
+      <c r="A26" s="57"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="62"/>
     </row>
     <row r="27" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="92"/>
-      <c r="B27" s="93"/>
-      <c r="C27" s="94"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="96"/>
-      <c r="F27" s="96"/>
-      <c r="G27" s="97"/>
-      <c r="H27" s="98"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="99"/>
-      <c r="L27" s="100"/>
+      <c r="A27" s="57"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="73"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="62"/>
     </row>
     <row r="28" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="98"/>
-      <c r="B28" s="93"/>
-      <c r="C28" s="94"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="96"/>
-      <c r="F28" s="96"/>
-      <c r="G28" s="97"/>
-      <c r="H28" s="98"/>
-      <c r="I28" s="99"/>
-      <c r="J28" s="99"/>
-      <c r="K28" s="99"/>
-      <c r="L28" s="100"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="62"/>
     </row>
     <row r="29" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="98"/>
-      <c r="B29" s="93"/>
-      <c r="C29" s="94"/>
-      <c r="D29" s="95"/>
-      <c r="E29" s="96"/>
-      <c r="F29" s="96"/>
-      <c r="G29" s="97"/>
-      <c r="H29" s="98"/>
-      <c r="I29" s="99"/>
-      <c r="J29" s="99"/>
-      <c r="K29" s="99"/>
-      <c r="L29" s="100"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="73"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="62"/>
     </row>
     <row r="30" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="98"/>
-      <c r="B30" s="93"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="97"/>
-      <c r="H30" s="98"/>
-      <c r="I30" s="99"/>
-      <c r="J30" s="99"/>
-      <c r="K30" s="99"/>
-      <c r="L30" s="100"/>
+      <c r="A30" s="61"/>
+      <c r="B30" s="64"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="73"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="62"/>
     </row>
     <row r="31" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="98"/>
-      <c r="B31" s="93"/>
-      <c r="C31" s="94"/>
-      <c r="D31" s="95"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="98"/>
-      <c r="I31" s="99"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="100"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="62"/>
     </row>
     <row r="32" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="98"/>
-      <c r="B32" s="93"/>
-      <c r="C32" s="94"/>
-      <c r="D32" s="95"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="97"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="99"/>
-      <c r="J32" s="99"/>
-      <c r="K32" s="99"/>
-      <c r="L32" s="100"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="64"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="62"/>
     </row>
     <row r="33" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="98"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="95"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="97"/>
-      <c r="H33" s="98"/>
-      <c r="I33" s="99"/>
-      <c r="J33" s="99"/>
-      <c r="K33" s="99"/>
-      <c r="L33" s="100"/>
+      <c r="A33" s="61"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="62"/>
     </row>
     <row r="34" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="98"/>
-      <c r="B34" s="93"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="103"/>
-      <c r="H34" s="98"/>
-      <c r="I34" s="99"/>
-      <c r="J34" s="99"/>
-      <c r="K34" s="99"/>
-      <c r="L34" s="100"/>
+      <c r="A34" s="61"/>
+      <c r="B34" s="64"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="73"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="62"/>
     </row>
     <row r="35" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="98"/>
-      <c r="B35" s="93"/>
-      <c r="C35" s="94"/>
-      <c r="D35" s="95"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="98"/>
-      <c r="I35" s="99"/>
-      <c r="J35" s="99"/>
-      <c r="K35" s="99"/>
-      <c r="L35" s="100"/>
+      <c r="A35" s="61"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="73"/>
+      <c r="J35" s="73"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="62"/>
     </row>
     <row r="36" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
@@ -1981,19 +1981,19 @@
       <c r="C39" s="29"/>
       <c r="D39" s="29"/>
       <c r="E39" s="29"/>
-      <c r="F39" s="54" t="s">
+      <c r="F39" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="G39" s="53" t="s">
+      <c r="G39" s="99" t="s">
         <v>30</v>
       </c>
       <c r="H39" s="1"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="55" t="s">
+      <c r="I39" s="103"/>
+      <c r="J39" s="103"/>
+      <c r="K39" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="L39" s="56"/>
+      <c r="L39" s="102"/>
     </row>
     <row r="40" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="31" t="s">
@@ -2003,13 +2003,13 @@
       <c r="C40" s="29"/>
       <c r="D40" s="29"/>
       <c r="E40" s="29"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="53"/>
+      <c r="F40" s="100"/>
+      <c r="G40" s="99"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="56"/>
+      <c r="I40" s="103"/>
+      <c r="J40" s="103"/>
+      <c r="K40" s="101"/>
+      <c r="L40" s="102"/>
     </row>
     <row r="41" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A41" s="30"/>
@@ -2026,31 +2026,31 @@
       <c r="L41" s="18"/>
     </row>
     <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="51" t="s">
+      <c r="A42" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
+      <c r="B42" s="97"/>
+      <c r="C42" s="97"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="97"/>
+      <c r="F42" s="97"/>
+      <c r="G42" s="98"/>
+      <c r="H42" s="98"/>
+      <c r="I42" s="98"/>
       <c r="J42" s="18"/>
       <c r="K42" s="18"/>
       <c r="L42" s="18"/>
     </row>
     <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="51"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="52"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="52"/>
+      <c r="A43" s="97"/>
+      <c r="B43" s="97"/>
+      <c r="C43" s="97"/>
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="97"/>
+      <c r="G43" s="98"/>
+      <c r="H43" s="98"/>
+      <c r="I43" s="98"/>
       <c r="J43" s="18"/>
       <c r="K43" s="18"/>
       <c r="L43" s="18"/>
@@ -2070,18 +2070,18 @@
       <c r="L44" s="18"/>
     </row>
     <row r="45" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="80" t="s">
+      <c r="A45" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="80"/>
+      <c r="B45" s="66"/>
       <c r="C45" s="48"/>
       <c r="D45" s="48"/>
       <c r="E45" s="49"/>
       <c r="F45" s="49"/>
-      <c r="G45" s="81" t="s">
+      <c r="G45" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="H45" s="81"/>
+      <c r="H45" s="67"/>
       <c r="I45" s="50" t="s">
         <v>41</v>
       </c>
@@ -2098,10 +2098,10 @@
       <c r="D46" s="48"/>
       <c r="E46" s="49"/>
       <c r="F46" s="49"/>
-      <c r="G46" s="77" t="s">
+      <c r="G46" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="H46" s="77"/>
+      <c r="H46" s="72"/>
       <c r="I46" s="50" t="s">
         <v>42</v>
       </c>
@@ -2124,23 +2124,68 @@
       <c r="L47" s="12"/>
     </row>
     <row r="48" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="67" t="s">
+      <c r="A48" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="67"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="67"/>
-      <c r="H48" s="67"/>
-      <c r="I48" s="67"/>
-      <c r="J48" s="67"/>
-      <c r="K48" s="67"/>
-      <c r="L48" s="67"/>
+      <c r="B48" s="83"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="83"/>
+      <c r="H48" s="83"/>
+      <c r="I48" s="83"/>
+      <c r="J48" s="83"/>
+      <c r="K48" s="83"/>
+      <c r="L48" s="83"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="tuc9YQKv5k37FwF0nmpDbZ36TupbY7aGLysJA7MMo+rqwzVPLg0sozqBrKN/xia7iiXK858gThg9gRLXw0P26w==" saltValue="75JITKSEvbIZdZUtYQyvzg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="60">
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="A42:F43"/>
+    <mergeCell ref="G42:I43"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E1:J4"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="D22:G22"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B34:C34"/>
@@ -2157,50 +2202,6 @@
     <mergeCell ref="D26:G26"/>
     <mergeCell ref="D27:G27"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E1:J4"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="A42:F43"/>
-    <mergeCell ref="G42:I43"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:G35"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
